--- a/01_requisitos/atividade.xlsx
+++ b/01_requisitos/atividade.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Desktop\K e M\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21C29331-1C8B-4CC3-B7B0-C11174616480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CB29525-F803-4E47-A1A2-66A63B361826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="3330" windowWidth="21600" windowHeight="11295" xr2:uid="{97B9CB19-41EB-471B-A4E4-B61DEB6E2891}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11295" xr2:uid="{97B9CB19-41EB-471B-A4E4-B61DEB6E2891}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
   <si>
     <t>Onde aparece</t>
   </si>
@@ -137,13 +137,133 @@
   </si>
   <si>
     <t>erro de formatação(sete )</t>
+  </si>
+  <si>
+    <t>perguntas</t>
+  </si>
+  <si>
+    <t>Entidades</t>
+  </si>
+  <si>
+    <t>(RD)</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>O preço unitário de venda de qualquer produto deve
+ ser um valor estritamente maior que zero.</t>
+  </si>
+  <si>
+    <t>O sistema deve armazenar, para cada
+ cliente, o ID único, nome completo
+ telefone e e-mail.</t>
+  </si>
+  <si>
+    <t>Animal</t>
+  </si>
+  <si>
+    <t>A quantidade de itens vendidos em uma operação
+ deve ser um número inteiro igual ou superior a 1.</t>
+  </si>
+  <si>
+    <t>O sistema deve associar cada animal a
+ exatamente um cliente responsável (tutor).</t>
+  </si>
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>Não é permitida a conclusão de uma venda sem que
+ um cliente esteja devidamente identificado no sistema.</t>
+  </si>
+  <si>
+    <t>O sistema deve registrar as informações de saúde
+ do animal, incluindo espécie, idade e restrições
+ médicas/alergias.</t>
+  </si>
+  <si>
+    <t>Fornecedor</t>
+  </si>
+  <si>
+    <t>O campo de espécies de animais deve aceitar apenas
+ opções previamente homologadas e padronizadas 
+(Ex: "Cão", "Gato").</t>
+  </si>
+  <si>
+    <t>O sistema deve cadastrar os produtos com código
+ identificador, descrição textual padronizada e preço
+ unitário padrão.</t>
+  </si>
+  <si>
+    <t>Venda</t>
+  </si>
+  <si>
+    <t>Sempre que a quantidade atual de um produto em
+ estoque ficar abaixo do estoque mínimo definido
+, o sistema deve emitir um alerta de reposição.</t>
+  </si>
+  <si>
+    <t>O sistema deve rastrear os níveis de estoque de cada
+produto, contendo quantidade atual e limite mínimo 
+de segurança.</t>
+  </si>
+  <si>
+    <t>Informações críticas de segurança, senhas externas
+ de clientes ou credenciais pessoais de e-mail nunca
+ devem ser armazenadas no banco de dados.</t>
+  </si>
+  <si>
+    <t>O sistema deve armazenar os dados 
+cadastrais do fornecedor de cada produto.</t>
+  </si>
+  <si>
+    <t>O sistema deve registrar a data e a hora exatas em
+ que cada venda foi realizada.</t>
+  </si>
+  <si>
+    <t>O sistema deve vincular obrigatoriamente um cliente
+ cadastrado a cada registro de venda.</t>
+  </si>
+  <si>
+    <t>O sistema deve armazenar os itens que compõem
+ uma venda, detalhando o produto, a quantidade
+ adquirida e o preço final aplicado.</t>
+  </si>
+  <si>
+    <t>O sistema deve registrar o histórico completo de
+ atendimentos e retornos agendados dos animais.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> O pet shop atende outras espécies de animais além de
+ cães e gatos? Existe uma lista fechada para cadastro?</t>
+  </si>
+  <si>
+    <t>Como o estabelecimento lida com descontos ou
+ promoções? O preço do produto pode variar por
+ cliente ou forma de pagamento?</t>
+  </si>
+  <si>
+    <t>(RN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Qual é o preço de tabela oficial da
+ "Ração Cão Adulto 10kg", considerando
+ as divergências encontradas de R$ 159,90 e R$ 169,90?</t>
+  </si>
+  <si>
+    <t>Qual é a idade correta do gato Mimi, pertencente ao tutor Pedro Nunes?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Qual é o valor padrão estipulado
+ para o estoque mínimo da "Ração Cão Adulto 10 KG"?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,10 +272,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -178,40 +310,203 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="11">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -227,12 +522,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3398628B-A0C5-4B59-A392-34890E5A383D}" name="Tabela1" displayName="Tabela1" ref="A1:C31" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="A1:C31" xr:uid="{3398628B-A0C5-4B59-A392-34890E5A383D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3398628B-A0C5-4B59-A392-34890E5A383D}" name="Tabela1" displayName="Tabela1" ref="A1:C18" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:C18" xr:uid="{3398628B-A0C5-4B59-A392-34890E5A383D}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{842A1AF0-799F-43A0-A2BD-FB1CF526C1E5}" name="Onde aparece" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{6DBC73DD-93E2-47BB-94CE-DA7E1917278E}" name="Problema encontrado" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{068AC7AC-43E4-46BD-B267-8172D6CC6BDE}" name="Tipo de problema" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{842A1AF0-799F-43A0-A2BD-FB1CF526C1E5}" name="Onde aparece" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{6DBC73DD-93E2-47BB-94CE-DA7E1917278E}" name="Problema encontrado" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{068AC7AC-43E4-46BD-B267-8172D6CC6BDE}" name="Tipo de problema" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5D2538DA-FAA4-4A41-8C02-21072EA894F7}" name="Tabela2" displayName="Tabela2" ref="E1:H19" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="E1:H19" xr:uid="{5D2538DA-FAA4-4A41-8C02-21072EA894F7}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{6954D99B-A420-4739-A940-D980894EAE68}" name="Entidades" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{B6D59866-CB36-4EA1-A86A-B963C849FA3A}" name="perguntas" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{BDDE4D63-332B-41E6-847D-878E5049C007}" name="(RD)" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{B63B59A3-2011-4C69-915A-2E2A83627505}" name="(RN)" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -535,269 +843,369 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1DB63B-4398-4C7F-87A2-385F937F7E3A}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
     <col min="2" max="2" width="36.140625" customWidth="1"/>
     <col min="3" max="3" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="62.7109375" customWidth="1"/>
+    <col min="7" max="7" width="48.140625" customWidth="1"/>
+    <col min="8" max="8" width="63.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="63" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="63" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="D4" s="2"/>
+      <c r="E4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="D5" s="2"/>
+      <c r="E5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>